--- a/nriss-patch-2/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$79</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2880" uniqueCount="489">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:15:45+00:00</t>
+    <t>2026-10-01T07:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -460,6 +460,26 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
+    <t>DiagnosticReport.extension:composition</t>
+  </si>
+  <si>
+    <t>composition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-composition-extension|0.1.0}
+</t>
+  </si>
+  <si>
+    <t>Composition du rapport d'imagerie</t>
+  </si>
+  <si>
+    <t>Composition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>DiagnosticReport.extension:comparaison</t>
   </si>
   <si>
@@ -476,10 +496,6 @@
     <t>Examen de comparaison radiologique</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>DiagnosticReport.extension:historiqueMedical</t>
   </si>
   <si>
@@ -506,7 +522,33 @@
     <t>Technique d'imagerie</t>
   </si>
   <si>
-    <t>Imaging procedure used for the imaging acquisition</t>
+    <t>Technique d'imagerie utilisée pour l'acquisition des images</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.extension:finding</t>
+  </si>
+  <si>
+    <t>finding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-finding-extension|0.1.0}
+</t>
+  </si>
+  <si>
+    <t>Résultats et observations cliniques de l'examen d'imagerie</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.extension:conclusion</t>
+  </si>
+  <si>
+    <t>conclusion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-conclusion-extension|0.1.0}
+</t>
+  </si>
+  <si>
+    <t>Conclusions cliniques et interprétations du rapport d'imagerie</t>
   </si>
   <si>
     <t>DiagnosticReport.modifierExtension</t>
@@ -590,7 +632,7 @@
     <t>This allows tracing of authorization for the report and tracking whether proposals/recommendations were acted upon.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:$this}
+    <t xml:space="preserve">type:$this}
 </t>
   </si>
   <si>
@@ -616,307 +658,10 @@
     <t>Référence à la demande d'examen contenant l'Accession Number</t>
   </si>
   <si>
-    <t>DiagnosticReport.status</t>
-  </si>
-  <si>
-    <t>Statut du compte-rendu d'imagerie</t>
-  </si>
-  <si>
-    <t>The status of the diagnostic report.</t>
-  </si>
-  <si>
-    <t>Diagnostic services routinely issue provisional/incomplete reports, and sometimes withdraw previously released reports.</t>
-  </si>
-  <si>
-    <t>final</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-report-status|4.0.1</t>
-  </si>
-  <si>
-    <t>Event.status</t>
-  </si>
-  <si>
-    <t>OBR-25 (not 1:1 mapping)</t>
-  </si>
-  <si>
-    <t>statusCode  Note: final and amended are distinguished by whether observation is the subject of a ControlAct event of type "revise"</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category</t>
-  </si>
-  <si>
-    <t>Department
-Sub-departmentServiceDiscipline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Type de résultat</t>
-  </si>
-  <si>
-    <t>A code that classifies the clinical discipline, department or diagnostic service that created the report (e.g. cardiology, biochemistry, hematology, MRI). This is used for searching, sorting and display purposes.</t>
-  </si>
-  <si>
-    <t>Multiple categories are allowed using various categorization schemes.   The level of granularity is defined by the category concepts in the value set. More fine-grained filtering can be performed using the metadata and/or terminology hierarchy in DiagnosticReport.code.</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="18748-4"/&gt;
-    &lt;display value="Imagerie"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-resultat-type-cisis|20260619134042</t>
-  </si>
-  <si>
-    <t>OBR-24</t>
-  </si>
-  <si>
-    <t>inboundRelationship[typeCode=COMP].source[classCode=LIST, moodCode=EVN, code &lt; LabService].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type
-</t>
-  </si>
-  <si>
-    <t>Type de document d'imagerie</t>
-  </si>
-  <si>
-    <t>A code or name that describes this diagnostic report.</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-code-document-imagerie-cisis|20260619134041</t>
-  </si>
-  <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>OBR-4 (HL7 v2 doesn't provide an easy way to indicate both the ordered test and the performed panel)</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.subject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patient
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-ins-document|0.1.0)
-</t>
-  </si>
-  <si>
-    <t>Patient concerné par le compte-rendu d'imagerie</t>
-  </si>
-  <si>
-    <t>The subject of the report. Usually, but not always, this is a patient. However, diagnostic services also perform analyses on specimens collected from a variety of other sources.</t>
-  </si>
-  <si>
-    <t>SHALL know the subject context.</t>
-  </si>
-  <si>
-    <t>Event.subject</t>
-  </si>
-  <si>
-    <t>PID-3 (no HL7 v2 mapping for Group or Device)</t>
-  </si>
-  <si>
-    <t>participation[typeCode=SBJ]</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.encounter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Context
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Health care event when test ordered</t>
-  </si>
-  <si>
-    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) which this DiagnosticReport is about.</t>
-  </si>
-  <si>
-    <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter  but still be tied to the context of the encounter  (e.g. pre-admission laboratory tests).</t>
-  </si>
-  <si>
-    <t>Links the request to the Encounter context.</t>
-  </si>
-  <si>
-    <t>Event.encounter</t>
-  </si>
-  <si>
-    <t>PV1-19</t>
-  </si>
-  <si>
-    <t>inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>FiveWs.context</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.effective[x]</t>
-  </si>
-  <si>
-    <t>Observation time
-Effective TimeOccurrence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>The time or time-period the observed values are related to. When the subject of the report is a patient, this is usually either the time of the procedure or of specimen collection(s), but very often the source of the date/time is not known, only the date/time itself.</t>
-  </si>
-  <si>
-    <t>If the diagnostic procedure was performed on the patient, this is the time it was performed. If there are specimens, the diagnostically relevant time can be derived from the specimen collection times, but the specimen information is not always available, and the exact relationship between the specimens and the diagnostically relevant time is not always automatic.</t>
-  </si>
-  <si>
-    <t>Need to know where in the patient history to file/present this report.</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>OBR-7</t>
-  </si>
-  <si>
-    <t>effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.issued</t>
-  </si>
-  <si>
-    <t>Date published
-Date IssuedDate Verified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>DateTime this version was made</t>
-  </si>
-  <si>
-    <t>The date and time that this version of the report was made available to providers, typically after the report was reviewed and verified.</t>
-  </si>
-  <si>
-    <t>May be different from the update time of the resource itself, because that is the status of the record (potentially a secondary copy), not the actual release time of the report.</t>
-  </si>
-  <si>
-    <t>Clinicians need to be able to check the date that the report was released.</t>
-  </si>
-  <si>
-    <t>OBR-22</t>
-  </si>
-  <si>
-    <t>participation[typeCode=VRF or AUT].time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer</t>
-  </si>
-  <si>
-    <t>Laboratory
-ServicePractitionerDepartmentCompanyAuthorized byDirector</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitioner-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-organization-document|0.1.0)
-</t>
-  </si>
-  <si>
-    <t>Exécutant</t>
-  </si>
-  <si>
-    <t>The diagnostic service that is responsible for issuing the report.</t>
-  </si>
-  <si>
-    <t>This is not necessarily the source of the atomic data items or the entity that interpreted the results. It is the entity that takes responsibility for the clinical report.</t>
-  </si>
-  <si>
-    <t>Need to know whom to contact if there are queries about the results. Also may need to track the source of reports for secondary data analysis.</t>
-  </si>
-  <si>
-    <t>Event.performer.actor</t>
-  </si>
-  <si>
-    <t>PRT-8 (where this PRT-4-Participation = "PO")</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=PRF]</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer:organization</t>
-  </si>
-  <si>
-    <t>organization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-organization-document|0.1.0)
-</t>
-  </si>
-  <si>
-    <t>Organization productrice du CR d'imagerie</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter</t>
-  </si>
-  <si>
-    <t>Analyzed by
-Reported by</t>
-  </si>
-  <si>
-    <t>Auteur</t>
-  </si>
-  <si>
-    <t>The practitioner or organization that is responsible for the report's conclusions and interpretations.</t>
-  </si>
-  <si>
-    <t>Might not be the same entity that takes responsibility for the clinical report.</t>
-  </si>
-  <si>
-    <t>OBR-32, PRT-8 (where this PRT-4-Participation = "PI")</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.id</t>
+    <t>DiagnosticReport.basedOn:serviceRequestAccessionNumber.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.basedOn.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -935,7 +680,16 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>DiagnosticReport.resultsInterpreter.extension</t>
+    <t>DiagnosticReport.basedOn:serviceRequestAccessionNumber.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.basedOn.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Extensions are always sliced by (at least) url</t>
@@ -944,157 +698,10 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:author</t>
-  </si>
-  <si>
-    <t>author</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-actor-extension|0.1.0}
-</t>
-  </si>
-  <si>
-    <t>Auteur du compte-rendu d'imagerie (Médecin - Radiologue)</t>
-  </si>
-  <si>
-    <t>Extension permettant de représenter un acteur impliqué dans le document avec son type et sa référence.</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:author.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:author.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension.extension</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:type</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:type.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension.extension.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:type.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension.extension.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:type.url</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:type.value[x]</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>AUT</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-actor-type-document|0.1.0</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:typeCode</t>
-  </si>
-  <si>
-    <t>typeCode</t>
-  </si>
-  <si>
-    <t>Type de participation</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:typeCode.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:typeCode.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:typeCode.url</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:typeCode.value[x]</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:actor</t>
-  </si>
-  <si>
-    <t>actor</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:actor.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:actor.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:actor.url</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:actor.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitionerRole-document|0.1.0)
-</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:author.url</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension.url</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-actor-extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension:author.value[x]</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.extension.value[x]</t>
-  </si>
-  <si>
-    <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter.reference</t>
+    <t>DiagnosticReport.basedOn:serviceRequestAccessionNumber.reference</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.basedOn.reference</t>
   </si>
   <si>
     <t>Literal reference, Relative, internal or absolute URL</t>
@@ -1113,7 +720,10 @@
 </t>
   </si>
   <si>
-    <t>DiagnosticReport.resultsInterpreter.type</t>
+    <t>DiagnosticReport.basedOn:serviceRequestAccessionNumber.type</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.basedOn.type</t>
   </si>
   <si>
     <t>Type the reference refers to (e.g. "Patient")</t>
@@ -1138,7 +748,14 @@
     <t>Reference.type</t>
   </si>
   <si>
-    <t>DiagnosticReport.resultsInterpreter.identifier</t>
+    <t>DiagnosticReport.basedOn:serviceRequestAccessionNumber.identifier</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.basedOn.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-accession-number-identifier-document|0.1.0}
+</t>
   </si>
   <si>
     <t>Logical reference, when literal reference is not known</t>
@@ -1159,29 +776,564 @@
     <t>.identifier</t>
   </si>
   <si>
+    <t>DiagnosticReport.basedOn:serviceRequestAccessionNumber.display</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.basedOn.display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.status</t>
+  </si>
+  <si>
+    <t>Statut du compte-rendu d'imagerie</t>
+  </si>
+  <si>
+    <t>The status of the diagnostic report.</t>
+  </si>
+  <si>
+    <t>Diagnostic services routinely issue provisional/incomplete reports, and sometimes withdraw previously released reports.</t>
+  </si>
+  <si>
+    <t>final</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-report-status|4.0.1</t>
+  </si>
+  <si>
+    <t>Event.status</t>
+  </si>
+  <si>
+    <t>OBR-25 (not 1:1 mapping)</t>
+  </si>
+  <si>
+    <t>statusCode  Note: final and amended are distinguished by whether observation is the subject of a ControlAct event of type "revise"</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category</t>
+  </si>
+  <si>
+    <t>Department
+Sub-departmentServiceDiscipline</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Type de résultat</t>
+  </si>
+  <si>
+    <t>A code that classifies the clinical discipline, department or diagnostic service that created the report (e.g. cardiology, biochemistry, hematology, MRI). This is used for searching, sorting and display purposes.</t>
+  </si>
+  <si>
+    <t>Multiple categories are allowed using various categorization schemes.   The level of granularity is defined by the category concepts in the value set. More fine-grained filtering can be performed using the metadata and/or terminology hierarchy in DiagnosticReport.code.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes for diagnostic service sections.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
+    <t>OBR-24</t>
+  </si>
+  <si>
+    <t>inboundRelationship[typeCode=COMP].source[classCode=LIST, moodCode=EVN, code &lt; LabService].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:typeResultat</t>
+  </si>
+  <si>
+    <t>typeResultat</t>
+  </si>
+  <si>
+    <t>Types de résultats</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-resultat-type-cisis|20260916095454</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:diagnostic-service</t>
+  </si>
+  <si>
+    <t>diagnostic-service</t>
+  </si>
+  <si>
+    <t>- **RAD** : Radiologie
+- **NMS** : Médecine nucléaire</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:imaging-report</t>
+  </si>
+  <si>
+    <t>imaging-report</t>
+  </si>
+  <si>
+    <t>définit la catégorie du rapport d'imagerie.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="85430-7"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:imaging</t>
+  </si>
+  <si>
+    <t>imaging</t>
+  </si>
+  <si>
+    <t>définit la catégorie de priorité du rapport</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://hl7.eu/fhir/health-data-api/CodeSystem/eehrxf-document-priority-category-cs"/&gt;
+    &lt;code value="Medical-Imaging"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type
+</t>
+  </si>
+  <si>
+    <t>Type de document d'imagerie (CR d'imagerie médicale, CR de médecine nucléaire)</t>
+  </si>
+  <si>
+    <t>A code or name that describes this diagnostic report.</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-value-set-imaging-report-type-document|0.1.0</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>OBR-4 (HL7 v2 doesn't provide an easy way to indicate both the ordered test and the performed panel)</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patient
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-ins-document|0.1.0)
+</t>
+  </si>
+  <si>
+    <t>Patient concerné par le compte-rendu d'imagerie</t>
+  </si>
+  <si>
+    <t>The subject of the report. Usually, but not always, this is a patient. However, diagnostic services also perform analyses on specimens collected from a variety of other sources.</t>
+  </si>
+  <si>
+    <t>SHALL know the subject context.</t>
+  </si>
+  <si>
+    <t>Event.subject</t>
+  </si>
+  <si>
+    <t>PID-3 (no HL7 v2 mapping for Group or Device)</t>
+  </si>
+  <si>
+    <t>participation[typeCode=SBJ]</t>
+  </si>
+  <si>
+    <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.encounter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Context
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-encounter-document|0.1.0)
+</t>
+  </si>
+  <si>
+    <t>L’événement de soins auquel se rapporte ce compte rendu de laboratoire (moment où l’examen a été prescrit).</t>
+  </si>
+  <si>
+    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) which this DiagnosticReport is about.</t>
+  </si>
+  <si>
+    <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter  but still be tied to the context of the encounter  (e.g. pre-admission laboratory tests).</t>
+  </si>
+  <si>
+    <t>Links the request to the Encounter context.</t>
+  </si>
+  <si>
+    <t>Event.encounter</t>
+  </si>
+  <si>
+    <t>PV1-19</t>
+  </si>
+  <si>
+    <t>inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>FiveWs.context</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.effective[x]</t>
+  </si>
+  <si>
+    <t>Observation time
+Effective TimeOccurrence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>The time or time-period the observed values are related to. When the subject of the report is a patient, this is usually either the time of the procedure or of specimen collection(s), but very often the source of the date/time is not known, only the date/time itself.</t>
+  </si>
+  <si>
+    <t>If the diagnostic procedure was performed on the patient, this is the time it was performed. If there are specimens, the diagnostically relevant time can be derived from the specimen collection times, but the specimen information is not always available, and the exact relationship between the specimens and the diagnostically relevant time is not always automatic.</t>
+  </si>
+  <si>
+    <t>Need to know where in the patient history to file/present this report.</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>OBR-7</t>
+  </si>
+  <si>
+    <t>effectiveTime</t>
+  </si>
+  <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.issued</t>
+  </si>
+  <si>
+    <t>Date published
+Date IssuedDate Verified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>DateTime this version was made</t>
+  </si>
+  <si>
+    <t>The date and time that this version of the report was made available to providers, typically after the report was reviewed and verified.</t>
+  </si>
+  <si>
+    <t>May be different from the update time of the resource itself, because that is the status of the record (potentially a secondary copy), not the actual release time of the report.</t>
+  </si>
+  <si>
+    <t>Clinicians need to be able to check the date that the report was released.</t>
+  </si>
+  <si>
+    <t>OBR-22</t>
+  </si>
+  <si>
+    <t>participation[typeCode=VRF or AUT].time</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.performer</t>
+  </si>
+  <si>
+    <t>Laboratory
+ServicePractitionerDepartmentCompanyAuthorized byDirector</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitioner-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-organization-document|0.1.0)
+</t>
+  </si>
+  <si>
+    <t>Exécutant</t>
+  </si>
+  <si>
+    <t>The diagnostic service that is responsible for issuing the report.</t>
+  </si>
+  <si>
+    <t>This is not necessarily the source of the atomic data items or the entity that interpreted the results. It is the entity that takes responsibility for the clinical report.</t>
+  </si>
+  <si>
+    <t>Need to know whom to contact if there are queries about the results. Also may need to track the source of reports for secondary data analysis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>Event.performer.actor</t>
+  </si>
+  <si>
+    <t>PRT-8 (where this PRT-4-Participation = "PO")</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=PRF]</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.performer:organization</t>
+  </si>
+  <si>
+    <t>organization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-organization-document|0.1.0)
+</t>
+  </si>
+  <si>
+    <t>Organization productrice du CR</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter</t>
+  </si>
+  <si>
+    <t>Analyzed by
+Reported by</t>
+  </si>
+  <si>
+    <t>Auteur</t>
+  </si>
+  <si>
+    <t>The practitioner or organization that is responsible for the report's conclusions and interpretations.</t>
+  </si>
+  <si>
+    <t>Might not be the same entity that takes responsibility for the clinical report.</t>
+  </si>
+  <si>
+    <t>OBR-32, PRT-8 (where this PRT-4-Participation = "PI")</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-actor-extension|0.1.0}
+</t>
+  </si>
+  <si>
+    <t>Auteur du compte-rendu d'imagerie (Médecin - Radiologue)</t>
+  </si>
+  <si>
+    <t>Extension permettant de représenter un acteur impliqué dans le document avec son type et sa référence.</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension.extension</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:type.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension.extension.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:type.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:type.url</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>AUT</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-actor-type-document|0.1.0</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:typeCode</t>
+  </si>
+  <si>
+    <t>typeCode</t>
+  </si>
+  <si>
+    <t>Type de participation</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:actor</t>
+  </si>
+  <si>
+    <t>actor</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:actor.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:actor.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:actor.url</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:actor.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitionerRole-document|0.1.0)
+</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.url</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension.url</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-actor-extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.value[x]</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.reference</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.type</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.identifier</t>
+  </si>
+  <si>
     <t>DiagnosticReport.resultsInterpreter.display</t>
   </si>
   <si>
-    <t>Text alternative for the resource</t>
-  </si>
-  <si>
-    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
-  </si>
-  <si>
-    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
-  </si>
-  <si>
-    <t>Reference.display</t>
-  </si>
-  <si>
     <t>DiagnosticReport.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen|4.0.1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-specimen-document|0.1.0)
 </t>
   </si>
   <si>
-    <t>Specimens this report is based on</t>
+    <t>Échantillons sur lesquels repose ce compte rendu.</t>
   </si>
   <si>
     <t>Details about the specimens on which this diagnostic report is based.</t>
@@ -1302,12 +1454,6 @@
     <t>DiagnosticReport.media.extension</t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
     <t>DiagnosticReport.media.modifierExtension</t>
   </si>
   <si>
@@ -1388,9 +1534,6 @@
   </si>
   <si>
     <t>One or more codes that represent the summary conclusion (interpretation/impression) of the diagnostic report.</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>Diagnosis codes provided as adjuncts to the report.</t>
@@ -1738,7 +1881,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN66"/>
+  <dimension ref="A1:AN79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="67.1484375" customWidth="true" bestFit="true"/>
@@ -1766,7 +1909,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="51.97265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="74.97265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="88.1953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -2713,7 +2856,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>79</v>
@@ -2825,10 +2968,10 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>91</v>
@@ -2960,7 +3103,7 @@
         <v>151</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3020,7 +3163,7 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>147</v>
+        <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>141</v>
@@ -3040,13 +3183,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>134</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>80</v>
@@ -3068,10 +3211,10 @@
         <v>80</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
         <v>156</v>
@@ -3134,7 +3277,7 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>147</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>141</v>
@@ -3152,16 +3295,18 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="D13" t="s" s="2">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3171,29 +3316,25 @@
         <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N13" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="O13" t="s" s="2">
-        <v>162</v>
-      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>80</v>
       </c>
@@ -3241,7 +3382,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3262,22 +3403,24 @@
         <v>80</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="D14" t="s" s="2">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3287,29 +3430,25 @@
         <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>80</v>
       </c>
@@ -3357,7 +3496,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3369,31 +3508,33 @@
         <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="D15" t="s" s="2">
-        <v>176</v>
+        <v>80</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3412,20 +3553,16 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>80</v>
       </c>
@@ -3461,17 +3598,19 @@
         <v>80</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AC15" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3483,16 +3622,16 @@
         <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>183</v>
+        <v>80</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>185</v>
+        <v>80</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>80</v>
@@ -3500,16 +3639,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3522,25 +3659,25 @@
         <v>80</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>188</v>
+        <v>135</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>80</v>
@@ -3589,7 +3726,7 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3601,60 +3738,62 @@
         <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>183</v>
+        <v>80</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>185</v>
+        <v>133</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>80</v>
+        <v>178</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>110</v>
+        <v>179</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O17" t="s" s="2">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -3664,7 +3803,7 @@
         <v>80</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>194</v>
+        <v>80</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>80</v>
@@ -3679,13 +3818,13 @@
         <v>80</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>195</v>
+        <v>80</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>192</v>
+        <v>80</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>196</v>
+        <v>80</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>80</v>
@@ -3703,13 +3842,13 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>80</v>
@@ -3718,32 +3857,32 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>200</v>
+        <v>187</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>79</v>
@@ -3755,21 +3894,23 @@
         <v>80</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
       </c>
@@ -3778,7 +3919,7 @@
         <v>80</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>207</v>
+        <v>80</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>80</v>
@@ -3793,29 +3934,29 @@
         <v>80</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Y18" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z18" t="s" s="2">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="AC18" s="2"/>
       <c r="AD18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3830,35 +3971,37 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>80</v>
+        <v>196</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>211</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="D19" t="s" s="2">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>80</v>
@@ -3867,19 +4010,23 @@
         <v>80</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
       </c>
@@ -3903,11 +4050,13 @@
         <v>80</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="Y19" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z19" t="s" s="2">
-        <v>216</v>
+        <v>80</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>80</v>
@@ -3925,13 +4074,13 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>80</v>
@@ -3940,28 +4089,28 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>220</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>222</v>
+        <v>80</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3977,21 +4126,19 @@
         <v>80</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="N20" s="2"/>
-      <c r="O20" t="s" s="2">
-        <v>226</v>
-      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>80</v>
       </c>
@@ -4039,7 +4186,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4051,38 +4198,38 @@
         <v>80</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>227</v>
+        <v>80</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>228</v>
+        <v>80</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>230</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>232</v>
+        <v>171</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>80</v>
@@ -4091,23 +4238,21 @@
         <v>80</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>233</v>
+        <v>135</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>237</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>80</v>
       </c>
@@ -4143,65 +4288,65 @@
         <v>80</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>80</v>
+        <v>214</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>238</v>
+        <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>239</v>
+        <v>80</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>240</v>
+        <v>209</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>241</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>243</v>
+        <v>80</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>80</v>
@@ -4210,20 +4355,18 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>244</v>
+        <v>205</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>13</v>
+        <v>218</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>245</v>
+        <v>219</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>80</v>
       </c>
@@ -4271,7 +4414,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4280,34 +4423,34 @@
         <v>90</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>80</v>
+        <v>222</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>248</v>
+        <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>249</v>
+        <v>80</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>250</v>
+        <v>133</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>251</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>252</v>
+        <v>223</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>252</v>
+        <v>224</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>253</v>
+        <v>80</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4326,20 +4469,18 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>254</v>
+        <v>104</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>255</v>
+        <v>225</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>80</v>
       </c>
@@ -4363,13 +4504,13 @@
         <v>80</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>80</v>
+        <v>228</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>80</v>
+        <v>229</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>80</v>
+        <v>230</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>80</v>
@@ -4387,7 +4528,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4405,35 +4546,35 @@
         <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>259</v>
+        <v>80</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>260</v>
+        <v>133</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>261</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>262</v>
+        <v>233</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>80</v>
@@ -4442,20 +4583,18 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>264</v>
+        <v>234</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>266</v>
+        <v>236</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>80</v>
       </c>
@@ -4491,23 +4630,25 @@
         <v>80</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AC24" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>80</v>
@@ -4516,40 +4657,38 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>269</v>
+        <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>270</v>
+        <v>80</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>271</v>
+        <v>239</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>272</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>273</v>
+        <v>240</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>80</v>
@@ -4558,20 +4697,18 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>275</v>
+        <v>205</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>80</v>
       </c>
@@ -4619,13 +4756,13 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>80</v>
@@ -4634,59 +4771,57 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>269</v>
+        <v>80</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>270</v>
+        <v>80</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>271</v>
+        <v>133</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>272</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>277</v>
+        <v>246</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>277</v>
+        <v>246</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>278</v>
+        <v>80</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>91</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>264</v>
+        <v>110</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>279</v>
+        <v>247</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -4696,7 +4831,7 @@
         <v>80</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>80</v>
@@ -4711,13 +4846,13 @@
         <v>80</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>80</v>
+        <v>251</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>80</v>
+        <v>248</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>80</v>
+        <v>252</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>80</v>
@@ -4735,13 +4870,13 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>277</v>
+        <v>246</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>80</v>
@@ -4750,55 +4885,57 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>282</v>
+        <v>254</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>272</v>
+        <v>256</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>80</v>
+        <v>258</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>78</v>
+        <v>259</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -4823,74 +4960,74 @@
         <v>80</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>80</v>
+        <v>265</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>80</v>
+        <v>266</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>287</v>
+        <v>257</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>80</v>
+        <v>268</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>80</v>
+        <v>270</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="D28" t="s" s="2">
-        <v>80</v>
+        <v>258</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>90</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>80</v>
@@ -4899,18 +5036,20 @@
         <v>80</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>135</v>
+        <v>260</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>136</v>
+        <v>273</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -4935,31 +5074,29 @@
         <v>80</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>80</v>
+        <v>274</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>290</v>
+        <v>80</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4971,60 +5108,62 @@
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>80</v>
+        <v>268</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>80</v>
+        <v>269</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>80</v>
+        <v>270</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>289</v>
+        <v>257</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>80</v>
+        <v>258</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>294</v>
+        <v>260</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>80</v>
@@ -5049,13 +5188,11 @@
         <v>80</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>80</v>
+        <v>266</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>80</v>
@@ -5073,7 +5210,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5085,58 +5222,62 @@
         <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>80</v>
+        <v>268</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>80</v>
+        <v>269</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>80</v>
+        <v>270</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>297</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="D30" t="s" s="2">
-        <v>80</v>
+        <v>258</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>80</v>
@@ -5146,7 +5287,7 @@
         <v>80</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>80</v>
+        <v>281</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>80</v>
@@ -5161,13 +5302,13 @@
         <v>80</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>80</v>
+        <v>265</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>80</v>
+        <v>266</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>80</v>
@@ -5185,70 +5326,74 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>287</v>
+        <v>257</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>80</v>
+        <v>268</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>80</v>
+        <v>270</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="D31" t="s" s="2">
-        <v>80</v>
+        <v>258</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>301</v>
+        <v>90</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>135</v>
+        <v>260</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>136</v>
+        <v>261</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>80</v>
@@ -5258,7 +5403,7 @@
         <v>80</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>80</v>
+        <v>285</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>80</v>
@@ -5273,31 +5418,31 @@
         <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>80</v>
+        <v>265</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>80</v>
+        <v>266</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>290</v>
+        <v>80</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5309,33 +5454,31 @@
         <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>80</v>
+        <v>268</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>80</v>
+        <v>269</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>80</v>
+        <v>270</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>80</v>
+        <v>287</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5351,16 +5494,16 @@
         <v>80</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>135</v>
+        <v>260</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>136</v>
+        <v>288</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>137</v>
+        <v>289</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5387,13 +5530,11 @@
         <v>80</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>80</v>
+        <v>290</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>80</v>
@@ -5411,71 +5552,73 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK32" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AG32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AL32" t="s" s="2">
-        <v>80</v>
+        <v>292</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>80</v>
+        <v>294</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>80</v>
+        <v>296</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+      <c r="O33" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
       </c>
@@ -5523,7 +5666,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5535,59 +5678,63 @@
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>80</v>
+        <v>301</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>80</v>
+        <v>302</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>80</v>
+        <v>306</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>135</v>
+        <v>307</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>136</v>
+        <v>308</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
       </c>
@@ -5623,55 +5770,55 @@
         <v>80</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>290</v>
+        <v>80</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>80</v>
+        <v>312</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>80</v>
+        <v>313</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>80</v>
+        <v>314</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>80</v>
+        <v>315</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>80</v>
+        <v>317</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5681,33 +5828,35 @@
         <v>90</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>104</v>
+        <v>318</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>310</v>
+        <v>13</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>303</v>
+        <v>80</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>80</v>
@@ -5749,10 +5898,10 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>90</v>
@@ -5761,31 +5910,31 @@
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>80</v>
+        <v>322</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>80</v>
+        <v>323</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>133</v>
+        <v>324</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>80</v>
+        <v>325</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>80</v>
+        <v>327</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5801,19 +5950,23 @@
         <v>80</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>110</v>
+        <v>328</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
@@ -5822,7 +5975,7 @@
         <v>80</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>318</v>
+        <v>80</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>80</v>
@@ -5837,11 +5990,13 @@
         <v>80</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="Y36" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z36" t="s" s="2">
-        <v>319</v>
+        <v>80</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>80</v>
@@ -5859,7 +6014,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5877,55 +6032,57 @@
         <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>80</v>
+        <v>333</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>133</v>
+        <v>334</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>80</v>
+        <v>335</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="C37" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>80</v>
+        <v>337</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>135</v>
+        <v>338</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
       </c>
@@ -5961,19 +6118,17 @@
         <v>80</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="AC37" s="2"/>
       <c r="AD37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>291</v>
+        <v>336</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5985,38 +6140,40 @@
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>80</v>
+        <v>344</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>80</v>
+        <v>345</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>80</v>
+        <v>346</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>80</v>
+        <v>347</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="D38" t="s" s="2">
-        <v>80</v>
+        <v>337</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>80</v>
@@ -6025,19 +6182,23 @@
         <v>80</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>284</v>
+        <v>350</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>285</v>
+        <v>351</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
       </c>
@@ -6085,71 +6246,75 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>287</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>80</v>
+        <v>344</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>80</v>
+        <v>345</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>288</v>
+        <v>346</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>80</v>
+        <v>347</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>325</v>
+        <v>352</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>307</v>
+        <v>352</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>80</v>
+        <v>353</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>135</v>
+        <v>338</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>136</v>
+        <v>354</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
       </c>
@@ -6185,19 +6350,19 @@
         <v>80</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>290</v>
+        <v>80</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>291</v>
+        <v>352</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6209,27 +6374,27 @@
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>80</v>
+        <v>344</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>80</v>
+        <v>357</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>80</v>
+        <v>346</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>80</v>
+        <v>347</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>309</v>
+        <v>358</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6237,7 +6402,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>90</v>
@@ -6252,24 +6417,22 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>104</v>
+        <v>205</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>310</v>
+        <v>206</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>322</v>
+        <v>80</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>80</v>
@@ -6311,10 +6474,10 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>313</v>
+        <v>208</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>90</v>
@@ -6332,7 +6495,7 @@
         <v>80</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>133</v>
+        <v>209</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>80</v>
@@ -6340,10 +6503,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>327</v>
+        <v>359</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>315</v>
+        <v>359</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6351,10 +6514,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>80</v>
@@ -6366,13 +6529,13 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>203</v>
+        <v>135</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>316</v>
+        <v>136</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>317</v>
+        <v>137</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6411,31 +6574,31 @@
         <v>80</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>80</v>
+        <v>214</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>320</v>
+        <v>215</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
@@ -6444,7 +6607,7 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>80</v>
@@ -6452,13 +6615,13 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>328</v>
+        <v>360</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>300</v>
+        <v>359</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>329</v>
+        <v>361</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>80</v>
@@ -6468,7 +6631,7 @@
         <v>90</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>80</v>
@@ -6480,13 +6643,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>135</v>
+        <v>362</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>136</v>
+        <v>363</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>137</v>
+        <v>364</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6537,7 +6700,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>291</v>
+        <v>215</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6566,10 +6729,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>305</v>
+        <v>366</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6592,13 +6755,13 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>284</v>
+        <v>205</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>285</v>
+        <v>206</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>286</v>
+        <v>207</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6649,7 +6812,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>287</v>
+        <v>208</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6670,7 +6833,7 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>288</v>
+        <v>209</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>80</v>
@@ -6678,10 +6841,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>307</v>
+        <v>368</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6689,10 +6852,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>369</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>80</v>
@@ -6752,7 +6915,7 @@
         <v>138</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>290</v>
+        <v>214</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>80</v>
@@ -6761,7 +6924,7 @@
         <v>139</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>291</v>
+        <v>215</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6790,12 +6953,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>332</v>
+        <v>370</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="C45" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="D45" t="s" s="2">
         <v>80</v>
       </c>
@@ -6816,24 +6981,22 @@
         <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>310</v>
+        <v>136</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>329</v>
+        <v>80</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>80</v>
@@ -6875,19 +7038,19 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>313</v>
+        <v>215</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
@@ -6896,7 +7059,7 @@
         <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>80</v>
@@ -6904,10 +7067,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>333</v>
+        <v>372</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>315</v>
+        <v>373</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6930,13 +7093,13 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>334</v>
+        <v>205</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>316</v>
+        <v>206</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>317</v>
+        <v>207</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6987,7 +7150,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>320</v>
+        <v>208</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6999,7 +7162,7 @@
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>80</v>
@@ -7008,7 +7171,7 @@
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>133</v>
+        <v>209</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>80</v>
@@ -7016,10 +7179,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>336</v>
+        <v>375</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7027,10 +7190,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>80</v>
@@ -7042,24 +7205,22 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>310</v>
+        <v>136</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>337</v>
+        <v>80</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>80</v>
@@ -7089,31 +7250,31 @@
         <v>80</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>80</v>
+        <v>214</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>313</v>
+        <v>215</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>80</v>
@@ -7122,7 +7283,7 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>80</v>
@@ -7130,10 +7291,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>338</v>
+        <v>376</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>339</v>
+        <v>377</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7141,10 +7302,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>80</v>
@@ -7156,22 +7317,24 @@
         <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>340</v>
+        <v>104</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>316</v>
+        <v>378</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>80</v>
+        <v>371</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>80</v>
@@ -7213,10 +7376,10 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>320</v>
+        <v>381</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>90</v>
@@ -7225,7 +7388,7 @@
         <v>80</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>80</v>
@@ -7242,10 +7405,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>341</v>
+        <v>382</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>341</v>
+        <v>383</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7265,20 +7428,18 @@
         <v>80</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>284</v>
+        <v>110</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>342</v>
+        <v>384</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>344</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -7288,7 +7449,7 @@
         <v>80</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>80</v>
+        <v>386</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>80</v>
@@ -7303,13 +7464,11 @@
         <v>80</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>80</v>
+        <v>387</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
@@ -7327,7 +7486,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>345</v>
+        <v>388</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7336,7 +7495,7 @@
         <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>346</v>
+        <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>102</v>
@@ -7356,12 +7515,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>347</v>
+        <v>389</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="D50" t="s" s="2">
         <v>80</v>
       </c>
@@ -7379,20 +7540,18 @@
         <v>80</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -7417,13 +7576,13 @@
         <v>80</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>351</v>
+        <v>80</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>352</v>
+        <v>80</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>353</v>
+        <v>80</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>80</v>
@@ -7441,19 +7600,19 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>354</v>
+        <v>215</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>80</v>
@@ -7462,7 +7621,7 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>80</v>
@@ -7470,10 +7629,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>355</v>
+        <v>392</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7493,20 +7652,18 @@
         <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>356</v>
+        <v>206</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -7555,7 +7712,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>359</v>
+        <v>208</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7567,7 +7724,7 @@
         <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>80</v>
@@ -7576,7 +7733,7 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>360</v>
+        <v>209</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -7584,10 +7741,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>361</v>
+        <v>393</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7598,7 +7755,7 @@
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>80</v>
@@ -7607,20 +7764,18 @@
         <v>80</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>284</v>
+        <v>135</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>362</v>
+        <v>136</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -7657,31 +7812,31 @@
         <v>80</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>80</v>
+        <v>214</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>365</v>
+        <v>215</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>80</v>
@@ -7690,7 +7845,7 @@
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -7698,10 +7853,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7709,10 +7864,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>80</v>
@@ -7724,26 +7879,24 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>367</v>
+        <v>104</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>371</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>80</v>
+        <v>390</v>
       </c>
       <c r="S53" t="s" s="2">
         <v>80</v>
@@ -7785,28 +7938,28 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>372</v>
+        <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>229</v>
+        <v>133</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>80</v>
@@ -7814,24 +7967,24 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>373</v>
+        <v>395</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>374</v>
+        <v>80</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>80</v>
@@ -7840,20 +7993,16 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>375</v>
+        <v>260</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>80</v>
       </c>
@@ -7889,23 +8038,25 @@
         <v>80</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AC54" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>80</v>
@@ -7917,37 +8068,37 @@
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>381</v>
+        <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>382</v>
+        <v>133</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>374</v>
+        <v>80</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>80</v>
@@ -7956,20 +8107,16 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>385</v>
+        <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>386</v>
+        <v>136</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>80</v>
       </c>
@@ -8017,7 +8164,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>373</v>
+        <v>215</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8029,33 +8176,31 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>381</v>
+        <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>382</v>
+        <v>80</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="C56" t="s" s="2">
-        <v>389</v>
-      </c>
+      <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>374</v>
+        <v>80</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8065,7 +8210,7 @@
         <v>90</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>80</v>
@@ -8074,20 +8219,16 @@
         <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>385</v>
+        <v>205</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>390</v>
+        <v>206</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>80</v>
       </c>
@@ -8135,28 +8276,28 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>373</v>
+        <v>208</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>381</v>
+        <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>382</v>
+        <v>209</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>80</v>
@@ -8164,10 +8305,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8178,7 +8319,7 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>80</v>
@@ -8190,17 +8331,15 @@
         <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>392</v>
+        <v>135</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>393</v>
+        <v>136</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8237,19 +8376,19 @@
         <v>80</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>80</v>
+        <v>214</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>391</v>
+        <v>215</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8261,7 +8400,7 @@
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>80</v>
@@ -8270,58 +8409,58 @@
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>396</v>
+        <v>80</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>397</v>
+        <v>377</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>398</v>
+        <v>80</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>399</v>
+        <v>104</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>400</v>
+        <v>378</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>80</v>
+        <v>397</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>80</v>
@@ -8363,28 +8502,28 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>403</v>
+        <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>382</v>
+        <v>133</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>80</v>
@@ -8392,10 +8531,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>404</v>
+        <v>383</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8418,13 +8557,13 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>284</v>
+        <v>402</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>285</v>
+        <v>384</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>286</v>
+        <v>385</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8475,7 +8614,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>287</v>
+        <v>388</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8487,7 +8626,7 @@
         <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>80</v>
@@ -8496,7 +8635,7 @@
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>288</v>
+        <v>133</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>80</v>
@@ -8504,21 +8643,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>80</v>
@@ -8530,16 +8669,16 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>406</v>
+        <v>378</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>407</v>
+        <v>379</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>161</v>
+        <v>380</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8547,7 +8686,7 @@
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>80</v>
+        <v>405</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>80</v>
@@ -8589,19 +8728,19 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>291</v>
+        <v>381</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>80</v>
@@ -8610,7 +8749,7 @@
         <v>80</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>288</v>
+        <v>133</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>80</v>
@@ -8618,46 +8757,42 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>409</v>
+        <v>80</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>135</v>
+        <v>408</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>80</v>
       </c>
@@ -8705,19 +8840,19 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>412</v>
+        <v>388</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>80</v>
@@ -8734,10 +8869,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8757,23 +8892,21 @@
         <v>80</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>284</v>
+        <v>205</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>414</v>
+        <v>218</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>415</v>
+        <v>219</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>80</v>
       </c>
@@ -8821,7 +8954,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>413</v>
+        <v>221</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8830,7 +8963,7 @@
         <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>80</v>
+        <v>222</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>102</v>
@@ -8842,18 +8975,18 @@
         <v>80</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>418</v>
+        <v>133</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8861,13 +8994,13 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>80</v>
@@ -8876,15 +9009,17 @@
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>420</v>
+        <v>104</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>421</v>
+        <v>225</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>80</v>
@@ -8909,13 +9044,13 @@
         <v>80</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>80</v>
+        <v>228</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>80</v>
+        <v>229</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>80</v>
+        <v>230</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>80</v>
@@ -8933,10 +9068,10 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>419</v>
+        <v>231</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>90</v>
@@ -8954,22 +9089,22 @@
         <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>423</v>
+        <v>133</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>425</v>
+        <v>80</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8979,27 +9114,27 @@
         <v>90</v>
       </c>
       <c r="H64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J64" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K64" t="s" s="2">
-        <v>284</v>
+        <v>179</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>426</v>
+        <v>235</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>80</v>
       </c>
@@ -9047,7 +9182,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>424</v>
+        <v>238</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9065,10 +9200,10 @@
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>429</v>
+        <v>80</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>430</v>
+        <v>239</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>80</v>
@@ -9076,10 +9211,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>431</v>
+        <v>412</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>431</v>
+        <v>412</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9090,7 +9225,7 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>80</v>
@@ -9099,18 +9234,20 @@
         <v>80</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>432</v>
+        <v>242</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -9135,13 +9272,13 @@
         <v>80</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>434</v>
+        <v>80</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>435</v>
+        <v>80</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>436</v>
+        <v>80</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>80</v>
@@ -9159,13 +9296,13 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>431</v>
+        <v>245</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>80</v>
@@ -9177,10 +9314,10 @@
         <v>80</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>429</v>
+        <v>80</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>437</v>
+        <v>133</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>80</v>
@@ -9188,10 +9325,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>438</v>
+        <v>413</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>438</v>
+        <v>413</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9199,10 +9336,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>91</v>
@@ -9214,19 +9351,19 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>439</v>
+        <v>414</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>440</v>
+        <v>415</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>441</v>
+        <v>416</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>442</v>
+        <v>417</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>443</v>
+        <v>418</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -9275,7 +9412,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>438</v>
+        <v>413</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9293,17 +9430,1507 @@
         <v>80</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AC67" s="2"/>
+      <c r="AD67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AN67" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="D68" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="D69" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AN66" t="s" s="2">
+      <c r="B71" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="P79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN66">
+  <autoFilter ref="A1:AN79">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9313,7 +10940,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI65">
+  <conditionalFormatting sqref="A2:AI78">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
